--- a/Game/cartridges/Asteroid Command/files/datasets/Shorthand Comments.xlsx
+++ b/Game/cartridges/Asteroid Command/files/datasets/Shorthand Comments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a442384f39a8593/(PCL)/Game/cartridges/Asteroid Command/files/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{709E3C53-85B5-467F-86EB-8BDB1EE3C8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689661A5-C2ED-46C2-9DEB-B34A3C8545B1}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{709E3C53-85B5-467F-86EB-8BDB1EE3C8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA5541A2-4017-4BD0-A448-D8ECB210B5A1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{397F63DF-7B5C-4906-BBF5-CC44F2F80C21}"/>
+    <workbookView xWindow="14303" yWindow="-3998" windowWidth="19394" windowHeight="11476" xr2:uid="{397F63DF-7B5C-4906-BBF5-CC44F2F80C21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>SH</t>
   </si>
@@ -219,16 +219,61 @@
   </si>
   <si>
     <t>Alert Status - Call being held due to vehicle count</t>
+  </si>
+  <si>
+    <t>LAM0</t>
+  </si>
+  <si>
+    <t>LAM1</t>
+  </si>
+  <si>
+    <t>LAM2</t>
+  </si>
+  <si>
+    <t>LAM3</t>
+  </si>
+  <si>
+    <t>LAM4</t>
+  </si>
+  <si>
+    <t>LAM5</t>
+  </si>
+  <si>
+    <t>Los Angeles Motor Scale - 0</t>
+  </si>
+  <si>
+    <t>Los Angeles Motor Scale - 1</t>
+  </si>
+  <si>
+    <t>Los Angeles Motor Scale - 2</t>
+  </si>
+  <si>
+    <t>Los Angeles Motor Scale - 3</t>
+  </si>
+  <si>
+    <t>Los Angeles Motor Scale - 4</t>
+  </si>
+  <si>
+    <t>Los Angeles Motor Scale - 5</t>
+  </si>
+  <si>
+    <t>Weight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -590,253 +635,410 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E2627CB-0C3D-42EE-BD70-CDD0874DD42E}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>42</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>46</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>50</v>
       </c>
       <c r="B27" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>51</v>
       </c>
       <c r="B28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>53</v>
       </c>
       <c r="B29" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>55</v>
       </c>
       <c r="B30" t="s">
         <v>56</v>
       </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>